--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-06-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%96%d7%99-%d7%a4%d7%99%d7%98%d7%a8%d7%a1-florescence/</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>החיים נראים מעט אחרת עבור מייזי פיטרס. מאז יציאת  אלבומה השני, "The Good Witch" מ-2023.  באלבומה השלישי, כוכבת הפופ הבריטית משחררת את הכאב ומוצאת שלווה באהבת אמת. בדיוק כשהקריירה שלה צברה תאוצה לקראת סוף 2024, הזמרת שנבחרה לחמם את ההופעות</v>
+        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
     </row>
   </sheetData>
